--- a/results/count/543_z13c1-2/measurements.xlsx
+++ b/results/count/543_z13c1-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,189 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v2-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1365.4667</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1138</v>
+      </c>
+      <c r="D6" t="n">
+        <v>591.7134</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>major_axis_length</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60.2958</v>
+      </c>
+      <c r="C7" t="n">
+        <v>47.4967</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21.4685</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>minor_axis_length</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>30.617</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31.6227</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.0558</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.7176</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7776999999999999</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9072</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>15</v>
       </c>
     </row>

--- a/results/count/543_z13c1-2/measurements.xlsx
+++ b/results/count/543_z13c1-2/measurements.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1365.4667</v>
+        <v>1862</v>
       </c>
       <c r="C6" t="n">
-        <v>1138</v>
+        <v>1736</v>
       </c>
       <c r="D6" t="n">
-        <v>591.7134</v>
+        <v>823.0119999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60.2958</v>
+        <v>78.36150000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>47.4967</v>
+        <v>74.0218</v>
       </c>
       <c r="D7" t="n">
-        <v>21.4685</v>
+        <v>22.3719</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.617</v>
+        <v>30.8137</v>
       </c>
       <c r="C8" t="n">
         <v>31.6227</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0558</v>
+        <v>6.9101</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.018</v>
+        <v>2.5873</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7176</v>
+        <v>2.6086</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.6752</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8013</v>
+        <v>0.9006</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.9236</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1377</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9072</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9227</v>
+        <v>0.9231</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0413</v>
+        <v>0.0388</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,31 +999,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1971</v>
+        <v>3069</v>
       </c>
       <c r="C9" t="n">
-        <v>75.8458</v>
+        <v>109.3585</v>
       </c>
       <c r="D9" t="n">
-        <v>35.522</v>
+        <v>37.084</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1352</v>
+        <v>2.9489</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8835</v>
+        <v>0.9407</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9025</v>
+        <v>0.9099</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1816</v>
+        <v>0.049</v>
       </c>
       <c r="I9" t="n">
-        <v>626.2608</v>
+        <v>642.6703</v>
       </c>
       <c r="J9" t="n">
-        <v>188.2207</v>
+        <v>188.3297</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1039,31 +1039,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1098</v>
+        <v>1616</v>
       </c>
       <c r="C10" t="n">
-        <v>41.5251</v>
+        <v>74.0218</v>
       </c>
       <c r="D10" t="n">
-        <v>36.5745</v>
+        <v>28.3763</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1354</v>
+        <v>2.6086</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4735</v>
+        <v>0.9236</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9165</v>
+        <v>0.9245</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3609</v>
+        <v>-0.0477</v>
       </c>
       <c r="I10" t="n">
-        <v>672.1266000000001</v>
+        <v>731.5359</v>
       </c>
       <c r="J10" t="n">
-        <v>188.5255</v>
+        <v>630.2376</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1079,31 +1079,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>895</v>
+        <v>1438</v>
       </c>
       <c r="C11" t="n">
-        <v>42.2519</v>
+        <v>72.50920000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>28.8189</v>
+        <v>25.5367</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4661</v>
+        <v>2.8394</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7313</v>
+        <v>0.9359</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9227</v>
+        <v>0.9236</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0393</v>
+        <v>0.0953</v>
       </c>
       <c r="I11" t="n">
-        <v>717.6101</v>
+        <v>793.1369999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>630.7162</v>
+        <v>478.379</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1119,196 +1119,36 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>721</v>
+        <v>3350</v>
       </c>
       <c r="C12" t="n">
-        <v>38.6871</v>
+        <v>107.7995</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4332</v>
+        <v>44.5116</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4636</v>
+        <v>2.4218</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7302</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9364</v>
+        <v>0.8475</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3362</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>748.8225</v>
+        <v>854.9167</v>
       </c>
       <c r="J12" t="n">
-        <v>629.6436</v>
+        <v>288.1039</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>622</v>
-      </c>
-      <c r="C13" t="n">
-        <v>36.1062</v>
-      </c>
-      <c r="D13" t="n">
-        <v>24.3339</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.4838</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.7388</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.9353</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3774</v>
-      </c>
-      <c r="I13" t="n">
-        <v>775.8407999999999</v>
-      </c>
-      <c r="J13" t="n">
-        <v>477.2605</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>816</v>
-      </c>
-      <c r="C14" t="n">
-        <v>43.1903</v>
-      </c>
-      <c r="D14" t="n">
-        <v>25.4434</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.6975</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8081</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1393</v>
-      </c>
-      <c r="I14" t="n">
-        <v>806.3211</v>
-      </c>
-      <c r="J14" t="n">
-        <v>479.2316</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1994</v>
-      </c>
-      <c r="C15" t="n">
-        <v>81.0461</v>
-      </c>
-      <c r="D15" t="n">
-        <v>40.4327</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.0045</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.2642</v>
-      </c>
-      <c r="I15" t="n">
-        <v>837.4136999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>288.6023</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1356</v>
-      </c>
-      <c r="C16" t="n">
-        <v>47.4967</v>
-      </c>
-      <c r="D16" t="n">
-        <v>38.2539</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.2416</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5927</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9307</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.2258</v>
-      </c>
-      <c r="I16" t="n">
-        <v>880.6549</v>
-      </c>
-      <c r="J16" t="n">
-        <v>287.3709</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>px</t>
         </is>
